--- a/docs/Client-Social-Media-Setup-Template.xlsx
+++ b/docs/Client-Social-Media-Setup-Template.xlsx
@@ -12,8 +12,27 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="H13" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Use an APP PASSWORD, not your account password.
+Bluesky: Settings → Privacy and security → App passwords.
+An app password can be revoked on its own without changing your login.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="120">
   <si>
     <t/>
   </si>
@@ -45,7 +64,19 @@
     <t>4.  Send the file back, or tell us and we will walk through it together on a call.</t>
   </si>
   <si>
-    <t>Please do NOT write account passwords in this file. We do not need them. We connect through each platform's official "sign in with…" screen, which you approve — your password is never shared. The only exception is Bluesky, which uses a revocable app password, explained on that row.</t>
+    <t>This file will contain passwords. Please handle it carefully: send it back through a method you trust, and once we confirm the accounts are set up, delete your copy. We will store our copy in a password manager and delete the spreadsheet.</t>
+  </si>
+  <si>
+    <t>Why we are asking for logins</t>
+  </si>
+  <si>
+    <t>We need them to CREATE and set up the accounts for you. Day-to-day publishing does not use them: once an account exists, you connect it by clicking "sign in with…" on the platform's own screen, and that approval is what lets us post. You can revoke it at any time without changing your password.</t>
+  </si>
+  <si>
+    <t>If you would rather create the accounts yourself, you can — just leave the password columns blank, fill in the usernames, and we will send you connection links instead.</t>
+  </si>
+  <si>
+    <t>One special case: Bluesky uses an APP PASSWORD rather than your real one. Instructions are on that row.</t>
   </si>
   <si>
     <t>Timelines to expect</t>
@@ -63,7 +94,7 @@
     <t>Questions? Reply to the email this came from and we will help.</t>
   </si>
   <si>
-    <t>Account Details — please complete the yellow column</t>
+    <t>Account Details — please complete the yellow columns</t>
   </si>
   <si>
     <t>Platform</t>
@@ -82,6 +113,15 @@
   </si>
   <si>
     <t>YOUR ANSWERS  ▼</t>
+  </si>
+  <si>
+    <t>Username / email  ▼</t>
+  </si>
+  <si>
+    <t>Password  ▼</t>
+  </si>
+  <si>
+    <t>2FA / recovery  ▼</t>
   </si>
   <si>
     <t>Done?</t>
@@ -469,7 +509,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,12 +533,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFD98A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF6F7F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF9E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -529,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -559,20 +609,26 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -582,13 +638,13 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -933,7 +989,7 @@
   <sheetPr>
     <tabColor rgb="FF0A1628"/>
   </sheetPr>
-  <dimension ref="A2:B21"/>
+  <dimension ref="A2:B26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1012,7 +1068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" ht="44" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1040,7 +1096,7 @@
       <c r="A18" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1048,7 +1104,7 @@
       <c r="A19" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1056,8 +1112,40 @@
       <c r="A21" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1159,7 @@
   <sheetPr>
     <tabColor rgb="FFF5C842"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1079,14 +1167,16 @@
     <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="46" customWidth="1"/>
-    <col min="6" max="6" width="42" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="62" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -1095,349 +1185,469 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
-    </row>
-    <row r="2" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" ht="68" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="H2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="I2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H3" s="12" t="s">
+      <c r="J2" s="8" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="K2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="12" t="s">
+    </row>
+    <row r="3" ht="68" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H4" s="12" t="s">
+      <c r="D3" s="14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="E3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="F3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="12" t="s">
+    </row>
+    <row r="4" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="B4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="D4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H5" s="12" t="s">
+      <c r="E4" s="13" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="F4" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="12" t="s">
+    </row>
+    <row r="5" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="B5" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12" t="s">
+      <c r="D5" s="14" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="E5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="F5" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="13" t="s">
+    </row>
+    <row r="6" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="B6" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="E6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="F6" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="13" t="s">
+    </row>
+    <row r="7" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="B7" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12" t="s">
+      <c r="D7" s="14" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="E7" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="13" t="s">
+      <c r="F7" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="12" t="s">
+    </row>
+    <row r="8" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12" t="s">
+      <c r="B8" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="D8" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="E8" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="F8" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K8" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12" t="s">
+    </row>
+    <row r="9" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="B9" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="12" t="s">
+      <c r="E9" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="F9" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="12" t="s">
+    </row>
+    <row r="10" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H11" s="12" t="s">
+      <c r="B10" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="12" ht="68" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="E10" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="F10" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="12" t="s">
+    </row>
+    <row r="11" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="B11" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="D11" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12" t="s">
+      <c r="E11" s="13" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="13" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="F11" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="13" t="s">
+    </row>
+    <row r="12" ht="68" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="B12" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="D12" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="E12" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="F12" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="12" t="s">
+    </row>
+    <row r="13" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12" t="s">
+      <c r="B13" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>84</v>
       </c>
+      <c r="E13" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>91</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H2"/>
+  <autoFilter ref="A2:K2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="G10:G14">
@@ -1463,6 +1673,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId14"/>
 </worksheet>
 </file>
 
@@ -1481,152 +1692,152 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>88</v>
+      <c r="A2" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>90</v>
+      <c r="A3" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>92</v>
+      <c r="A4" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>94</v>
+      <c r="A5" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>96</v>
+      <c r="A6" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>98</v>
+      <c r="A7" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>100</v>
+      <c r="A8" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>102</v>
+      <c r="A9" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>104</v>
+      <c r="A10" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>106</v>
+      <c r="A11" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>108</v>
+      <c r="A12" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>110</v>
+      <c r="A13" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>112</v>
+      <c r="A14" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
